--- a/data/general.xlsx
+++ b/data/general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/04 Abril/Dasboatdde marzo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{827E7EFF-C44D-46D5-AA95-E9E6C6768738}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{D38F4008-6566-4043-A2A6-318D4F91697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530565D9-7F75-4E4C-9F2E-CE9581CC78F3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F008453E-1A06-40CE-9AA2-8079F823278A}"/>
   </bookViews>
@@ -789,10 +789,12 @@
       <c r="N2" s="16">
         <v>1500</v>
       </c>
-      <c r="O2" s="16"/>
+      <c r="O2" s="16">
+        <v>1170</v>
+      </c>
       <c r="P2" s="18">
         <f>O2/N2</f>
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="Q2" s="16">
         <v>95</v>
@@ -857,7 +859,9 @@
       <c r="N3" s="16">
         <v>0</v>
       </c>
-      <c r="O3" s="16"/>
+      <c r="O3" s="16">
+        <v>0</v>
+      </c>
       <c r="P3" s="18">
         <v>0</v>
       </c>
@@ -924,10 +928,12 @@
       <c r="N4" s="16">
         <v>800</v>
       </c>
-      <c r="O4" s="16"/>
+      <c r="O4" s="16">
+        <v>865</v>
+      </c>
       <c r="P4" s="18">
         <f t="shared" ref="P4:P24" si="1">O4/N4</f>
-        <v>0</v>
+        <v>1.08125</v>
       </c>
       <c r="Q4" s="16">
         <v>135</v>
@@ -992,10 +998,12 @@
       <c r="N5" s="16">
         <v>1200</v>
       </c>
-      <c r="O5" s="16"/>
+      <c r="O5" s="16">
+        <v>936</v>
+      </c>
       <c r="P5" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="Q5" s="16">
         <v>69</v>
@@ -1060,10 +1068,12 @@
       <c r="N6" s="16">
         <v>1200</v>
       </c>
-      <c r="O6" s="16"/>
+      <c r="O6" s="16">
+        <v>1156</v>
+      </c>
       <c r="P6" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.96333333333333337</v>
       </c>
       <c r="Q6" s="16">
         <v>68</v>
@@ -1128,10 +1138,12 @@
       <c r="N7" s="16">
         <v>1500</v>
       </c>
-      <c r="O7" s="16"/>
+      <c r="O7" s="16">
+        <v>1423</v>
+      </c>
       <c r="P7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.94866666666666666</v>
       </c>
       <c r="Q7" s="16">
         <v>176</v>
@@ -1196,10 +1208,12 @@
       <c r="N8" s="16">
         <v>1500</v>
       </c>
-      <c r="O8" s="16"/>
+      <c r="O8" s="16">
+        <v>578</v>
+      </c>
       <c r="P8" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.38533333333333336</v>
       </c>
       <c r="Q8" s="16">
         <v>98</v>
@@ -1264,10 +1278,12 @@
       <c r="N9" s="16">
         <v>1200</v>
       </c>
-      <c r="O9" s="16"/>
+      <c r="O9" s="16">
+        <v>1202</v>
+      </c>
       <c r="P9" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0016666666666667</v>
       </c>
       <c r="Q9" s="16">
         <v>128</v>
@@ -1332,10 +1348,12 @@
       <c r="N10" s="16">
         <v>1200</v>
       </c>
-      <c r="O10" s="16"/>
+      <c r="O10" s="16">
+        <v>964</v>
+      </c>
       <c r="P10" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.80333333333333334</v>
       </c>
       <c r="Q10" s="16">
         <v>54</v>
@@ -1400,10 +1418,12 @@
       <c r="N11" s="16">
         <v>800</v>
       </c>
-      <c r="O11" s="16"/>
+      <c r="O11" s="16">
+        <v>553</v>
+      </c>
       <c r="P11" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.69125000000000003</v>
       </c>
       <c r="Q11" s="16">
         <v>60</v>
@@ -1468,10 +1488,12 @@
       <c r="N12" s="16">
         <v>1200</v>
       </c>
-      <c r="O12" s="16"/>
+      <c r="O12" s="16">
+        <v>317</v>
+      </c>
       <c r="P12" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.26416666666666666</v>
       </c>
       <c r="Q12" s="16">
         <v>74</v>
@@ -1536,10 +1558,12 @@
       <c r="N13" s="16">
         <v>1200</v>
       </c>
-      <c r="O13" s="16"/>
+      <c r="O13" s="16">
+        <v>1029</v>
+      </c>
       <c r="P13" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.85750000000000004</v>
       </c>
       <c r="Q13" s="16">
         <v>183</v>
@@ -1604,10 +1628,12 @@
       <c r="N14" s="16">
         <v>1200</v>
       </c>
-      <c r="O14" s="16"/>
+      <c r="O14" s="16">
+        <v>1074</v>
+      </c>
       <c r="P14" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="Q14" s="16">
         <v>168</v>
@@ -1672,10 +1698,12 @@
       <c r="N15" s="16">
         <v>1200</v>
       </c>
-      <c r="O15" s="16"/>
+      <c r="O15" s="16">
+        <v>1014</v>
+      </c>
       <c r="P15" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="Q15" s="16">
         <v>92</v>
@@ -1740,10 +1768,12 @@
       <c r="N16" s="16">
         <v>1500</v>
       </c>
-      <c r="O16" s="16"/>
+      <c r="O16" s="16">
+        <v>1730</v>
+      </c>
       <c r="P16" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1533333333333333</v>
       </c>
       <c r="Q16" s="16">
         <v>129</v>
@@ -1808,10 +1838,12 @@
       <c r="N17" s="16">
         <v>1500</v>
       </c>
-      <c r="O17" s="16"/>
+      <c r="O17" s="16">
+        <v>1559</v>
+      </c>
       <c r="P17" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0393333333333334</v>
       </c>
       <c r="Q17" s="16">
         <v>183</v>
@@ -1876,10 +1908,12 @@
       <c r="N18" s="16">
         <v>1500</v>
       </c>
-      <c r="O18" s="16"/>
+      <c r="O18" s="16">
+        <v>1507</v>
+      </c>
       <c r="P18" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0046666666666666</v>
       </c>
       <c r="Q18" s="16">
         <v>146</v>
@@ -1944,10 +1978,12 @@
       <c r="N19" s="16">
         <v>1500</v>
       </c>
-      <c r="O19" s="16"/>
+      <c r="O19" s="16">
+        <v>1442</v>
+      </c>
       <c r="P19" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.96133333333333337</v>
       </c>
       <c r="Q19" s="16">
         <v>198</v>
@@ -2012,10 +2048,12 @@
       <c r="N20" s="16">
         <v>1500</v>
       </c>
-      <c r="O20" s="16"/>
+      <c r="O20" s="16">
+        <v>1454</v>
+      </c>
       <c r="P20" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.96933333333333338</v>
       </c>
       <c r="Q20" s="16">
         <v>151</v>
@@ -2080,10 +2118,12 @@
       <c r="N21" s="16">
         <v>1500</v>
       </c>
-      <c r="O21" s="16"/>
+      <c r="O21" s="16">
+        <v>940</v>
+      </c>
       <c r="P21" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.62666666666666671</v>
       </c>
       <c r="Q21" s="16">
         <v>192</v>
@@ -2148,10 +2188,12 @@
       <c r="N22" s="16">
         <v>1500</v>
       </c>
-      <c r="O22" s="16"/>
+      <c r="O22" s="16">
+        <v>1514</v>
+      </c>
       <c r="P22" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0093333333333334</v>
       </c>
       <c r="Q22" s="16">
         <v>181</v>
@@ -2216,10 +2258,12 @@
       <c r="N23" s="16">
         <v>1500</v>
       </c>
-      <c r="O23" s="16"/>
+      <c r="O23" s="16">
+        <v>1537</v>
+      </c>
       <c r="P23" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0246666666666666</v>
       </c>
       <c r="Q23" s="16">
         <v>126</v>
@@ -2299,11 +2343,11 @@
       </c>
       <c r="O24" s="20">
         <f>SUM(O2:O23)</f>
-        <v>0</v>
+        <v>23964</v>
       </c>
       <c r="P24" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.86512635379061376</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(Q2:Q23)</f>
